--- a/示例/案例B-订单流水统计/运行成果/订单流水统计分析结果_示例.xlsx
+++ b/示例/案例B-订单流水统计/运行成果/订单流水统计分析结果_示例.xlsx
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTA(原始数据!$A$3:$A$32)</f>
+        <f>COUNTA(原始数据!$D$3:$D$32)</f>
         <v>30</v>
       </c>
     </row>

--- a/示例/案例B-订单流水统计/运行成果/订单流水统计分析结果_示例.xlsx
+++ b/示例/案例B-订单流水统计/运行成果/订单流水统计分析结果_示例.xlsx
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTA(原始数据!$D$3:$D$32)</f>
+        <f>COUNTA(原始数据!$A$3:$A$32)</f>
         <v>30</v>
       </c>
     </row>
